--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536500.3266925947</v>
+        <v>536500</v>
       </c>
       <c r="R2" t="n">
-        <v>6908762.731328222</v>
+        <v>6908763</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2008-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,34 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84181916</v>
+        <v>84181923</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>97524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -779,6 +775,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>84181916</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Näsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6908763</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>DIN200808191445</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2008-08-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2008-08-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Surdråg i granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Wannberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84181923</v>
+        <v>84181916</v>
       </c>
       <c r="B2" t="n">
-        <v>97524</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -782,34 +786,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84181916</v>
+        <v>84181923</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>97977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22470-2024 artfynd.xlsx
+++ b/artfynd/A 22470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>